--- a/app/loading/data/imports/Import_Status_With_IDs.xlsx
+++ b/app/loading/data/imports/Import_Status_With_IDs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\internship\erp-fastapi\app\loading\data\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E387AFBB-18BF-4376-A6C3-41B1D5350BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0B2FE3-95E3-472F-B006-94C67079E245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5097,9 +5097,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5408,6 +5409,10 @@
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="6" max="6" width="29.140625" customWidth="1"/>
     <col min="8" max="8" width="42.28515625" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" customWidth="1"/>
+    <col min="13" max="13" width="28.42578125" customWidth="1"/>
+    <col min="19" max="19" width="23" style="2" customWidth="1"/>
+    <col min="21" max="21" width="21.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:105" x14ac:dyDescent="0.25">
@@ -5465,13 +5470,13 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="V1" t="s">
@@ -7006,10 +7011,10 @@
       <c r="P11" t="s">
         <v>191</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S11" s="2">
         <v>46077</v>
       </c>
-      <c r="U11" s="1">
+      <c r="U11" s="2">
         <v>46166</v>
       </c>
       <c r="V11">
@@ -7161,10 +7166,10 @@
       <c r="P12" t="s">
         <v>191</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S12" s="2">
         <v>46077</v>
       </c>
-      <c r="U12" s="1">
+      <c r="U12" s="2">
         <v>46166</v>
       </c>
       <c r="V12">
@@ -7396,10 +7401,10 @@
       <c r="P14" t="s">
         <v>191</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S14" s="2">
         <v>45953</v>
       </c>
-      <c r="U14" s="1">
+      <c r="U14" s="2">
         <v>46045</v>
       </c>
       <c r="V14">
@@ -7750,10 +7755,10 @@
       <c r="R17">
         <v>12.464</v>
       </c>
-      <c r="S17" s="1">
+      <c r="S17" s="2">
         <v>46002</v>
       </c>
-      <c r="U17" s="1">
+      <c r="U17" s="2">
         <v>46086</v>
       </c>
       <c r="V17">
@@ -7983,10 +7988,10 @@
       <c r="R18">
         <v>8.1769999999999996</v>
       </c>
-      <c r="S18" s="1">
+      <c r="S18" s="2">
         <v>46002</v>
       </c>
-      <c r="U18" s="1">
+      <c r="U18" s="2">
         <v>46086</v>
       </c>
       <c r="V18">
@@ -8216,10 +8221,10 @@
       <c r="R19">
         <v>7.6340000000000003</v>
       </c>
-      <c r="S19" s="1">
+      <c r="S19" s="2">
         <v>46002</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U19" s="2">
         <v>46086</v>
       </c>
       <c r="V19">
@@ -8449,10 +8454,10 @@
       <c r="R20">
         <v>11.231999999999999</v>
       </c>
-      <c r="S20" s="1">
+      <c r="S20" s="2">
         <v>46002</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20" s="2">
         <v>46086</v>
       </c>
       <c r="V20">
@@ -8682,10 +8687,10 @@
       <c r="R21">
         <v>10.507</v>
       </c>
-      <c r="S21" s="1">
+      <c r="S21" s="2">
         <v>46002</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21" s="2">
         <v>46086</v>
       </c>
       <c r="V21">
@@ -8915,10 +8920,10 @@
       <c r="R22">
         <v>4.0570000000000004</v>
       </c>
-      <c r="S22" s="1">
+      <c r="S22" s="2">
         <v>46002</v>
       </c>
-      <c r="U22" s="1">
+      <c r="U22" s="2">
         <v>46086</v>
       </c>
       <c r="V22">
@@ -9148,10 +9153,10 @@
       <c r="R23">
         <v>21.11</v>
       </c>
-      <c r="S23" s="1">
+      <c r="S23" s="2">
         <v>46002</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>46086</v>
       </c>
       <c r="V23">
@@ -9736,10 +9741,10 @@
       <c r="P26" t="s">
         <v>191</v>
       </c>
-      <c r="S26" s="1">
+      <c r="S26" s="2">
         <v>45957</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>46050</v>
       </c>
       <c r="V26">
@@ -9939,10 +9944,10 @@
       <c r="P27" t="s">
         <v>191</v>
       </c>
-      <c r="S27" s="1">
+      <c r="S27" s="2">
         <v>45957</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U27" s="2">
         <v>46050</v>
       </c>
       <c r="V27">
@@ -11287,10 +11292,10 @@
       <c r="P35" t="s">
         <v>109</v>
       </c>
-      <c r="S35" s="1">
+      <c r="S35" s="2">
         <v>45967</v>
       </c>
-      <c r="U35" s="1">
+      <c r="U35" s="2">
         <v>46059</v>
       </c>
       <c r="V35">
@@ -11490,10 +11495,10 @@
       <c r="P36" t="s">
         <v>109</v>
       </c>
-      <c r="S36" s="1">
+      <c r="S36" s="2">
         <v>45957</v>
       </c>
-      <c r="U36" s="1">
+      <c r="U36" s="2">
         <v>46048</v>
       </c>
       <c r="V36">
@@ -11687,10 +11692,10 @@
       <c r="P37" t="s">
         <v>109</v>
       </c>
-      <c r="S37" s="1">
+      <c r="S37" s="2">
         <v>45967</v>
       </c>
-      <c r="U37" s="1">
+      <c r="U37" s="2">
         <v>46059</v>
       </c>
       <c r="V37">
@@ -11884,10 +11889,10 @@
       <c r="P38" t="s">
         <v>109</v>
       </c>
-      <c r="S38" s="1">
+      <c r="S38" s="2">
         <v>45967</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>46059</v>
       </c>
       <c r="V38">
@@ -12081,10 +12086,10 @@
       <c r="P39" t="s">
         <v>109</v>
       </c>
-      <c r="S39" s="1">
+      <c r="S39" s="2">
         <v>45967</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U39" s="2">
         <v>46059</v>
       </c>
       <c r="V39">
@@ -12450,10 +12455,10 @@
       <c r="R42">
         <v>13.832000000000001</v>
       </c>
-      <c r="S42" s="1">
+      <c r="S42" s="2">
         <v>46163</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U42" s="2">
         <v>46247</v>
       </c>
       <c r="V42">
@@ -12647,10 +12652,10 @@
       <c r="R43">
         <v>11.302199999999999</v>
       </c>
-      <c r="S43" s="1">
+      <c r="S43" s="2">
         <v>46163</v>
       </c>
-      <c r="U43" s="1">
+      <c r="U43" s="2">
         <v>46247</v>
       </c>
       <c r="V43">
@@ -12838,10 +12843,10 @@
       <c r="R44">
         <v>8.0440000000000005</v>
       </c>
-      <c r="S44" s="1">
+      <c r="S44" s="2">
         <v>46163</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U44" s="2">
         <v>46247</v>
       </c>
       <c r="V44">
@@ -13032,10 +13037,10 @@
       <c r="R45">
         <v>0.28000000000000003</v>
       </c>
-      <c r="S45" s="1">
+      <c r="S45" s="2">
         <v>46163</v>
       </c>
-      <c r="U45" s="1">
+      <c r="U45" s="2">
         <v>46247</v>
       </c>
       <c r="V45">
@@ -13226,10 +13231,10 @@
       <c r="R46">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="S46" s="1">
+      <c r="S46" s="2">
         <v>46163</v>
       </c>
-      <c r="U46" s="1">
+      <c r="U46" s="2">
         <v>46247</v>
       </c>
       <c r="V46">
@@ -13417,10 +13422,10 @@
       <c r="R47">
         <v>27.68</v>
       </c>
-      <c r="S47" s="1">
+      <c r="S47" s="2">
         <v>46157</v>
       </c>
-      <c r="U47" s="1">
+      <c r="U47" s="2">
         <v>46241</v>
       </c>
       <c r="V47">
@@ -13614,10 +13619,10 @@
       <c r="R48">
         <v>3.266</v>
       </c>
-      <c r="S48" s="1">
+      <c r="S48" s="2">
         <v>46157</v>
       </c>
-      <c r="U48" s="1">
+      <c r="U48" s="2">
         <v>46241</v>
       </c>
       <c r="V48">
@@ -13805,10 +13810,10 @@
       <c r="R49">
         <v>5.6159999999999997</v>
       </c>
-      <c r="S49" s="1">
+      <c r="S49" s="2">
         <v>46157</v>
       </c>
-      <c r="U49" s="1">
+      <c r="U49" s="2">
         <v>46241</v>
       </c>
       <c r="V49">
@@ -13996,10 +14001,10 @@
       <c r="R50">
         <v>1.2270000000000001</v>
       </c>
-      <c r="S50" s="1">
+      <c r="S50" s="2">
         <v>46160</v>
       </c>
-      <c r="U50" s="1">
+      <c r="U50" s="2">
         <v>46244</v>
       </c>
       <c r="V50">
@@ -14190,10 +14195,10 @@
       <c r="R51">
         <v>1.2270000000000001</v>
       </c>
-      <c r="S51" s="1">
+      <c r="S51" s="2">
         <v>46160</v>
       </c>
-      <c r="U51" s="1">
+      <c r="U51" s="2">
         <v>46244</v>
       </c>
       <c r="V51">
@@ -14384,10 +14389,10 @@
       <c r="R52">
         <v>5.1050000000000004</v>
       </c>
-      <c r="S52" s="1">
+      <c r="S52" s="2">
         <v>46161</v>
       </c>
-      <c r="U52" s="1">
+      <c r="U52" s="2">
         <v>46246</v>
       </c>
       <c r="V52">
@@ -14575,10 +14580,10 @@
       <c r="R53">
         <v>4.1340000000000003</v>
       </c>
-      <c r="S53" s="1">
+      <c r="S53" s="2">
         <v>46149</v>
       </c>
-      <c r="U53" s="1">
+      <c r="U53" s="2">
         <v>46233</v>
       </c>
       <c r="V53">
@@ -14763,10 +14768,10 @@
       <c r="R54">
         <v>2.5579999999999998</v>
       </c>
-      <c r="S54" s="1">
+      <c r="S54" s="2">
         <v>46153</v>
       </c>
-      <c r="U54" s="1">
+      <c r="U54" s="2">
         <v>46237</v>
       </c>
       <c r="V54">
@@ -14954,10 +14959,10 @@
       <c r="R55">
         <v>14.234</v>
       </c>
-      <c r="S55" s="1">
+      <c r="S55" s="2">
         <v>46156</v>
       </c>
-      <c r="U55" s="1">
+      <c r="U55" s="2">
         <v>46242</v>
       </c>
       <c r="V55">
@@ -15145,10 +15150,10 @@
       <c r="R56">
         <v>12.491</v>
       </c>
-      <c r="S56" s="1">
+      <c r="S56" s="2">
         <v>46156</v>
       </c>
-      <c r="U56" s="1">
+      <c r="U56" s="2">
         <v>46242</v>
       </c>
       <c r="V56">
@@ -15336,10 +15341,10 @@
       <c r="R57">
         <v>24.981999999999999</v>
       </c>
-      <c r="S57" s="1">
+      <c r="S57" s="2">
         <v>46157</v>
       </c>
-      <c r="U57" s="1">
+      <c r="U57" s="2">
         <v>46241</v>
       </c>
       <c r="V57">
@@ -15527,10 +15532,10 @@
       <c r="R58">
         <v>7.38</v>
       </c>
-      <c r="S58" s="1">
+      <c r="S58" s="2">
         <v>46140</v>
       </c>
-      <c r="U58" s="1">
+      <c r="U58" s="2">
         <v>46224</v>
       </c>
       <c r="V58">
@@ -15730,10 +15735,10 @@
       <c r="R59">
         <v>28.05</v>
       </c>
-      <c r="S59" s="1">
+      <c r="S59" s="2">
         <v>46140</v>
       </c>
-      <c r="U59" s="1">
+      <c r="U59" s="2">
         <v>46224</v>
       </c>
       <c r="V59">
@@ -15933,10 +15938,10 @@
       <c r="R60">
         <v>6.3780000000000001</v>
       </c>
-      <c r="S60" s="1">
+      <c r="S60" s="2">
         <v>46146</v>
       </c>
-      <c r="U60" s="1">
+      <c r="U60" s="2">
         <v>46231</v>
       </c>
       <c r="V60">
@@ -16136,10 +16141,10 @@
       <c r="R61">
         <v>6.3780000000000001</v>
       </c>
-      <c r="S61" s="1">
+      <c r="S61" s="2">
         <v>46146</v>
       </c>
-      <c r="U61" s="1">
+      <c r="U61" s="2">
         <v>46231</v>
       </c>
       <c r="V61">
@@ -16339,10 +16344,10 @@
       <c r="R62">
         <v>6.2640000000000002</v>
       </c>
-      <c r="S62" s="1">
+      <c r="S62" s="2">
         <v>46136</v>
       </c>
-      <c r="U62" s="1">
+      <c r="U62" s="2">
         <v>46220</v>
       </c>
       <c r="V62">
@@ -16530,10 +16535,10 @@
       <c r="R63">
         <v>16.565999999999999</v>
       </c>
-      <c r="S63" s="1">
+      <c r="S63" s="2">
         <v>46136</v>
       </c>
-      <c r="U63" s="1">
+      <c r="U63" s="2">
         <v>46220</v>
       </c>
       <c r="V63">
@@ -16715,10 +16720,10 @@
       <c r="R64">
         <v>1.2945</v>
       </c>
-      <c r="S64" s="1">
+      <c r="S64" s="2">
         <v>46136</v>
       </c>
-      <c r="U64" s="1">
+      <c r="U64" s="2">
         <v>46220</v>
       </c>
       <c r="V64">
@@ -16915,10 +16920,10 @@
       <c r="R65">
         <v>1.3342000000000001</v>
       </c>
-      <c r="S65" s="1">
+      <c r="S65" s="2">
         <v>46136</v>
       </c>
-      <c r="U65" s="1">
+      <c r="U65" s="2">
         <v>46220</v>
       </c>
       <c r="V65">
@@ -17109,10 +17114,10 @@
       <c r="R66">
         <v>1.3537999999999999</v>
       </c>
-      <c r="S66" s="1">
+      <c r="S66" s="2">
         <v>46136</v>
       </c>
-      <c r="U66" s="1">
+      <c r="U66" s="2">
         <v>46220</v>
       </c>
       <c r="V66">
@@ -17303,10 +17308,10 @@
       <c r="R67">
         <v>1.2355</v>
       </c>
-      <c r="S67" s="1">
+      <c r="S67" s="2">
         <v>46136</v>
       </c>
-      <c r="U67" s="1">
+      <c r="U67" s="2">
         <v>46220</v>
       </c>
       <c r="V67">
@@ -17500,10 +17505,10 @@
       <c r="R68">
         <v>4.8518999999999997</v>
       </c>
-      <c r="S68" s="1">
+      <c r="S68" s="2">
         <v>46139</v>
       </c>
-      <c r="U68" s="1">
+      <c r="U68" s="2">
         <v>46223</v>
       </c>
       <c r="V68">
@@ -18207,10 +18212,10 @@
       <c r="R72">
         <v>15.893000000000001</v>
       </c>
-      <c r="S72" s="1">
+      <c r="S72" s="2">
         <v>46126</v>
       </c>
-      <c r="U72" s="1">
+      <c r="U72" s="2">
         <v>46210</v>
       </c>
       <c r="V72">
@@ -18419,10 +18424,10 @@
       <c r="R73">
         <v>15.11</v>
       </c>
-      <c r="S73" s="1">
+      <c r="S73" s="2">
         <v>46126</v>
       </c>
-      <c r="U73" s="1">
+      <c r="U73" s="2">
         <v>46210</v>
       </c>
       <c r="V73">
@@ -18625,10 +18630,10 @@
       <c r="R74">
         <v>8.2260000000000009</v>
       </c>
-      <c r="S74" s="1">
+      <c r="S74" s="2">
         <v>46126</v>
       </c>
-      <c r="U74" s="1">
+      <c r="U74" s="2">
         <v>46210</v>
       </c>
       <c r="V74">
@@ -18831,10 +18836,10 @@
       <c r="R75">
         <v>8.2949999999999999</v>
       </c>
-      <c r="S75" s="1">
+      <c r="S75" s="2">
         <v>46129</v>
       </c>
-      <c r="U75" s="1">
+      <c r="U75" s="2">
         <v>46213</v>
       </c>
       <c r="V75">
@@ -19040,10 +19045,10 @@
       <c r="R76">
         <v>1.452</v>
       </c>
-      <c r="S76" s="1">
+      <c r="S76" s="2">
         <v>46122</v>
       </c>
-      <c r="U76" s="1">
+      <c r="U76" s="2">
         <v>46208</v>
       </c>
       <c r="V76">
@@ -19252,10 +19257,10 @@
       <c r="R77">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="S77" s="1">
+      <c r="S77" s="2">
         <v>46122</v>
       </c>
-      <c r="U77" s="1">
+      <c r="U77" s="2">
         <v>46208</v>
       </c>
       <c r="V77">
@@ -19514,10 +19519,10 @@
       <c r="P79" t="s">
         <v>286</v>
       </c>
-      <c r="S79" s="1">
+      <c r="S79" s="2">
         <v>46106</v>
       </c>
-      <c r="U79" s="1">
+      <c r="U79" s="2">
         <v>46198</v>
       </c>
       <c r="V79">
@@ -19729,10 +19734,10 @@
       <c r="R80">
         <v>5.3879999999999999</v>
       </c>
-      <c r="S80" s="1">
+      <c r="S80" s="2">
         <v>46115</v>
       </c>
-      <c r="U80" s="1">
+      <c r="U80" s="2">
         <v>46203</v>
       </c>
       <c r="V80">
@@ -19929,10 +19934,10 @@
       <c r="R81">
         <v>3.73</v>
       </c>
-      <c r="S81" s="1">
+      <c r="S81" s="2">
         <v>46115</v>
       </c>
-      <c r="U81" s="1">
+      <c r="U81" s="2">
         <v>46203</v>
       </c>
       <c r="V81">
@@ -20129,10 +20134,10 @@
       <c r="R82">
         <v>66.391000000000005</v>
       </c>
-      <c r="S82" s="1">
+      <c r="S82" s="2">
         <v>46115</v>
       </c>
-      <c r="U82" s="1">
+      <c r="U82" s="2">
         <v>46203</v>
       </c>
       <c r="V82">
@@ -20335,10 +20340,10 @@
       <c r="R83">
         <v>10.76</v>
       </c>
-      <c r="S83" s="1">
+      <c r="S83" s="2">
         <v>46115</v>
       </c>
-      <c r="U83" s="1">
+      <c r="U83" s="2">
         <v>46203</v>
       </c>
       <c r="V83">
@@ -20535,10 +20540,10 @@
       <c r="R84">
         <v>63.33</v>
       </c>
-      <c r="S84" s="1">
+      <c r="S84" s="2">
         <v>46115</v>
       </c>
-      <c r="U84" s="1">
+      <c r="U84" s="2">
         <v>46203</v>
       </c>
       <c r="V84">
@@ -20735,10 +20740,10 @@
       <c r="R85">
         <v>6.3760000000000003</v>
       </c>
-      <c r="S85" s="1">
+      <c r="S85" s="2">
         <v>46115</v>
       </c>
-      <c r="U85" s="1">
+      <c r="U85" s="2">
         <v>46203</v>
       </c>
       <c r="V85">
@@ -20991,10 +20996,10 @@
       <c r="P87" t="s">
         <v>286</v>
       </c>
-      <c r="S87" s="1">
+      <c r="S87" s="2">
         <v>46106</v>
       </c>
-      <c r="U87" s="1">
+      <c r="U87" s="2">
         <v>46228</v>
       </c>
       <c r="V87">
@@ -21188,10 +21193,10 @@
       <c r="P88" t="s">
         <v>286</v>
       </c>
-      <c r="S88" s="1">
+      <c r="S88" s="2">
         <v>46078</v>
       </c>
-      <c r="U88" s="1">
+      <c r="U88" s="2">
         <v>46167</v>
       </c>
       <c r="V88">
@@ -21379,10 +21384,10 @@
       <c r="P89" t="s">
         <v>286</v>
       </c>
-      <c r="S89" s="1">
+      <c r="S89" s="2">
         <v>46106</v>
       </c>
-      <c r="U89" s="1">
+      <c r="U89" s="2">
         <v>46198</v>
       </c>
       <c r="V89">
@@ -21570,10 +21575,10 @@
       <c r="P90" t="s">
         <v>286</v>
       </c>
-      <c r="S90" s="1">
+      <c r="S90" s="2">
         <v>46106</v>
       </c>
-      <c r="U90" s="1">
+      <c r="U90" s="2">
         <v>46198</v>
       </c>
       <c r="V90">
@@ -21761,10 +21766,10 @@
       <c r="P91" t="s">
         <v>199</v>
       </c>
-      <c r="S91" s="1">
+      <c r="S91" s="2">
         <v>46185</v>
       </c>
-      <c r="U91" s="1">
+      <c r="U91" s="2">
         <v>46209</v>
       </c>
       <c r="W91" t="s">
@@ -21919,10 +21924,10 @@
       <c r="P92" t="s">
         <v>199</v>
       </c>
-      <c r="S92" s="1">
+      <c r="S92" s="2">
         <v>46162</v>
       </c>
-      <c r="U92" s="1">
+      <c r="U92" s="2">
         <v>46254</v>
       </c>
       <c r="W92" t="s">
@@ -22083,10 +22088,10 @@
       <c r="R93">
         <v>8.5399999999999991</v>
       </c>
-      <c r="S93" s="1">
+      <c r="S93" s="2">
         <v>46100</v>
       </c>
-      <c r="U93" s="1">
+      <c r="U93" s="2">
         <v>46184</v>
       </c>
       <c r="V93">
@@ -22295,10 +22300,10 @@
       <c r="R94">
         <v>41.52</v>
       </c>
-      <c r="S94" s="1">
+      <c r="S94" s="2">
         <v>46115</v>
       </c>
-      <c r="U94" s="1">
+      <c r="U94" s="2">
         <v>46203</v>
       </c>
       <c r="V94">
@@ -22501,10 +22506,10 @@
       <c r="R95">
         <v>2.92</v>
       </c>
-      <c r="S95" s="1">
+      <c r="S95" s="2">
         <v>46115</v>
       </c>
-      <c r="U95" s="1">
+      <c r="U95" s="2">
         <v>46203</v>
       </c>
       <c r="V95">
@@ -23247,10 +23252,10 @@
       <c r="R102">
         <v>4.4039999999999999</v>
       </c>
-      <c r="S102" s="1">
+      <c r="S102" s="2">
         <v>46051</v>
       </c>
-      <c r="U102" s="1">
+      <c r="U102" s="2">
         <v>46162</v>
       </c>
       <c r="V102">
@@ -23474,10 +23479,10 @@
       <c r="R103">
         <v>9.2870000000000008</v>
       </c>
-      <c r="S103" s="1">
+      <c r="S103" s="2">
         <v>46057</v>
       </c>
-      <c r="U103" s="1">
+      <c r="U103" s="2">
         <v>46168</v>
       </c>
       <c r="V103">
@@ -23698,10 +23703,10 @@
       <c r="R104">
         <v>4.1929999999999996</v>
       </c>
-      <c r="S104" s="1">
+      <c r="S104" s="2">
         <v>46051</v>
       </c>
-      <c r="U104" s="1">
+      <c r="U104" s="2">
         <v>46162</v>
       </c>
       <c r="V104">
@@ -23916,10 +23921,10 @@
       <c r="R105">
         <v>12.44</v>
       </c>
-      <c r="S105" s="1">
+      <c r="S105" s="2">
         <v>46072</v>
       </c>
-      <c r="U105" s="1">
+      <c r="U105" s="2">
         <v>46179</v>
       </c>
       <c r="V105">
@@ -24301,10 +24306,10 @@
       <c r="P107" t="s">
         <v>286</v>
       </c>
-      <c r="S107" s="1">
+      <c r="S107" s="2">
         <v>46035</v>
       </c>
-      <c r="U107" s="1">
+      <c r="U107" s="2">
         <v>46125</v>
       </c>
       <c r="V107">
@@ -24501,10 +24506,10 @@
       <c r="P108" t="s">
         <v>286</v>
       </c>
-      <c r="S108" s="1">
+      <c r="S108" s="2">
         <v>46035</v>
       </c>
-      <c r="U108" s="1">
+      <c r="U108" s="2">
         <v>46125</v>
       </c>
       <c r="V108">
@@ -24701,10 +24706,10 @@
       <c r="P109" t="s">
         <v>286</v>
       </c>
-      <c r="S109" s="1">
+      <c r="S109" s="2">
         <v>46035</v>
       </c>
-      <c r="U109" s="1">
+      <c r="U109" s="2">
         <v>46125</v>
       </c>
       <c r="V109">
@@ -24901,10 +24906,10 @@
       <c r="P110" t="s">
         <v>286</v>
       </c>
-      <c r="S110" s="1">
+      <c r="S110" s="2">
         <v>46049</v>
       </c>
-      <c r="U110" s="1">
+      <c r="U110" s="2">
         <v>46139</v>
       </c>
       <c r="V110">
@@ -26199,10 +26204,10 @@
       <c r="P117" t="s">
         <v>191</v>
       </c>
-      <c r="S117" s="1">
+      <c r="S117" s="2">
         <v>45982</v>
       </c>
-      <c r="U117" s="1">
+      <c r="U117" s="2">
         <v>46074</v>
       </c>
       <c r="V117">
@@ -26327,10 +26332,10 @@
       <c r="R118">
         <v>21.6</v>
       </c>
-      <c r="S118" s="1">
+      <c r="S118" s="2">
         <v>45953</v>
       </c>
-      <c r="U118" s="1">
+      <c r="U118" s="2">
         <v>46045</v>
       </c>
       <c r="V118">
@@ -26530,10 +26535,10 @@
       <c r="R119">
         <v>430</v>
       </c>
-      <c r="S119" s="1">
+      <c r="S119" s="2">
         <v>45972</v>
       </c>
-      <c r="U119" s="1">
+      <c r="U119" s="2">
         <v>46058</v>
       </c>
       <c r="V119">
@@ -26998,10 +27003,10 @@
       <c r="P122" t="s">
         <v>191</v>
       </c>
-      <c r="S122" s="1">
+      <c r="S122" s="2">
         <v>45986</v>
       </c>
-      <c r="U122" s="1">
+      <c r="U122" s="2">
         <v>46074</v>
       </c>
       <c r="V122">
@@ -27192,10 +27197,10 @@
       <c r="P123" t="s">
         <v>109</v>
       </c>
-      <c r="S123" s="1">
+      <c r="S123" s="2">
         <v>45982</v>
       </c>
-      <c r="U123" s="1">
+      <c r="U123" s="2">
         <v>46074</v>
       </c>
       <c r="V123">
@@ -27395,7 +27400,7 @@
       <c r="P124" t="s">
         <v>109</v>
       </c>
-      <c r="S124" s="1">
+      <c r="S124" s="2">
         <v>45967</v>
       </c>
       <c r="V124">
@@ -27583,7 +27588,7 @@
       <c r="P125" t="s">
         <v>109</v>
       </c>
-      <c r="S125" s="1">
+      <c r="S125" s="2">
         <v>45967</v>
       </c>
       <c r="V125">
@@ -27765,7 +27770,7 @@
       <c r="P126" t="s">
         <v>109</v>
       </c>
-      <c r="S126" s="1">
+      <c r="S126" s="2">
         <v>45967</v>
       </c>
       <c r="V126">
@@ -27947,7 +27952,7 @@
       <c r="P127" t="s">
         <v>109</v>
       </c>
-      <c r="S127" s="1">
+      <c r="S127" s="2">
         <v>45967</v>
       </c>
       <c r="V127">
@@ -28129,7 +28134,7 @@
       <c r="P128" t="s">
         <v>109</v>
       </c>
-      <c r="S128" s="1">
+      <c r="S128" s="2">
         <v>45967</v>
       </c>
       <c r="V128">
@@ -28317,7 +28322,7 @@
       <c r="P129" t="s">
         <v>109</v>
       </c>
-      <c r="S129" s="1">
+      <c r="S129" s="2">
         <v>45979</v>
       </c>
       <c r="V129">
@@ -28505,7 +28510,7 @@
       <c r="P130" t="s">
         <v>109</v>
       </c>
-      <c r="S130" s="1">
+      <c r="S130" s="2">
         <v>45979</v>
       </c>
       <c r="V130">
@@ -28693,7 +28698,7 @@
       <c r="P131" t="s">
         <v>109</v>
       </c>
-      <c r="S131" s="1">
+      <c r="S131" s="2">
         <v>45979</v>
       </c>
       <c r="V131">
@@ -30462,10 +30467,10 @@
       <c r="P141" t="s">
         <v>109</v>
       </c>
-      <c r="S141" s="1">
+      <c r="S141" s="2">
         <v>46106</v>
       </c>
-      <c r="U141" s="1">
+      <c r="U141" s="2">
         <v>46198</v>
       </c>
       <c r="V141">
@@ -30656,10 +30661,10 @@
       <c r="P142" t="s">
         <v>109</v>
       </c>
-      <c r="S142" s="1">
+      <c r="S142" s="2">
         <v>46090</v>
       </c>
-      <c r="U142" s="1">
+      <c r="U142" s="2">
         <v>46174</v>
       </c>
       <c r="V142">
@@ -35406,10 +35411,10 @@
       <c r="P171" t="s">
         <v>191</v>
       </c>
-      <c r="S171" s="1">
+      <c r="S171" s="2">
         <v>46077</v>
       </c>
-      <c r="U171" s="1">
+      <c r="U171" s="2">
         <v>46166</v>
       </c>
       <c r="W171" t="s">
@@ -35976,10 +35981,10 @@
       <c r="P174" t="s">
         <v>191</v>
       </c>
-      <c r="S174" s="1">
+      <c r="S174" s="2">
         <v>46087</v>
       </c>
-      <c r="U174" s="1">
+      <c r="U174" s="2">
         <v>46129</v>
       </c>
       <c r="V174">
@@ -36146,10 +36151,10 @@
       <c r="P175" t="s">
         <v>286</v>
       </c>
-      <c r="S175" s="1">
+      <c r="S175" s="2">
         <v>46005</v>
       </c>
-      <c r="U175" s="1">
+      <c r="U175" s="2">
         <v>46104</v>
       </c>
       <c r="V175">
@@ -36346,10 +36351,10 @@
       <c r="P176" t="s">
         <v>191</v>
       </c>
-      <c r="S176" s="1">
+      <c r="S176" s="2">
         <v>46091</v>
       </c>
-      <c r="U176" s="1">
+      <c r="U176" s="2">
         <v>46184</v>
       </c>
       <c r="V176">
@@ -36528,10 +36533,10 @@
       <c r="P177" t="s">
         <v>109</v>
       </c>
-      <c r="S177" s="1">
+      <c r="S177" s="2">
         <v>46077</v>
       </c>
-      <c r="U177" s="1">
+      <c r="U177" s="2">
         <v>46166</v>
       </c>
       <c r="V177">
@@ -36716,10 +36721,10 @@
       <c r="P178" t="s">
         <v>109</v>
       </c>
-      <c r="S178" s="1">
+      <c r="S178" s="2">
         <v>46063</v>
       </c>
-      <c r="U178" s="1">
+      <c r="U178" s="2">
         <v>46152</v>
       </c>
       <c r="V178">
@@ -36898,10 +36903,10 @@
       <c r="P179" t="s">
         <v>109</v>
       </c>
-      <c r="S179" s="1">
+      <c r="S179" s="2">
         <v>46077</v>
       </c>
-      <c r="U179" s="1">
+      <c r="U179" s="2">
         <v>46166</v>
       </c>
       <c r="V179">
@@ -37080,10 +37085,10 @@
       <c r="P180" t="s">
         <v>191</v>
       </c>
-      <c r="S180" s="1">
+      <c r="S180" s="2">
         <v>46077</v>
       </c>
-      <c r="U180" s="1">
+      <c r="U180" s="2">
         <v>46166</v>
       </c>
       <c r="V180">
@@ -37280,10 +37285,10 @@
       <c r="P181" t="s">
         <v>191</v>
       </c>
-      <c r="S181" s="1">
+      <c r="S181" s="2">
         <v>46035</v>
       </c>
-      <c r="U181" s="1">
+      <c r="U181" s="2">
         <v>46125</v>
       </c>
       <c r="V181">
@@ -37483,10 +37488,10 @@
       <c r="P182" t="s">
         <v>191</v>
       </c>
-      <c r="S182" s="1">
+      <c r="S182" s="2">
         <v>46035</v>
       </c>
-      <c r="U182" s="1">
+      <c r="U182" s="2">
         <v>46125</v>
       </c>
       <c r="V182">
@@ -37680,10 +37685,10 @@
       <c r="P183" t="s">
         <v>191</v>
       </c>
-      <c r="S183" s="1">
+      <c r="S183" s="2">
         <v>46049</v>
       </c>
-      <c r="U183" s="1">
+      <c r="U183" s="2">
         <v>46139</v>
       </c>
       <c r="V183">
@@ -37877,10 +37882,10 @@
       <c r="P184" t="s">
         <v>109</v>
       </c>
-      <c r="S184" s="1">
+      <c r="S184" s="2">
         <v>46049</v>
       </c>
-      <c r="U184" s="1">
+      <c r="U184" s="2">
         <v>46139</v>
       </c>
       <c r="W184" t="s">
@@ -38074,10 +38079,10 @@
       <c r="P185" t="s">
         <v>109</v>
       </c>
-      <c r="S185" s="1">
+      <c r="S185" s="2">
         <v>46049</v>
       </c>
-      <c r="U185" s="1">
+      <c r="U185" s="2">
         <v>46139</v>
       </c>
       <c r="W185" t="s">
@@ -38265,10 +38270,10 @@
       <c r="P186" t="s">
         <v>109</v>
       </c>
-      <c r="S186" s="1">
+      <c r="S186" s="2">
         <v>46049</v>
       </c>
-      <c r="U186" s="1">
+      <c r="U186" s="2">
         <v>46139</v>
       </c>
       <c r="W186" t="s">
@@ -38456,10 +38461,10 @@
       <c r="P187" t="s">
         <v>109</v>
       </c>
-      <c r="S187" s="1">
+      <c r="S187" s="2">
         <v>46049</v>
       </c>
-      <c r="U187" s="1">
+      <c r="U187" s="2">
         <v>46139</v>
       </c>
       <c r="W187" t="s">
@@ -38647,10 +38652,10 @@
       <c r="P188" t="s">
         <v>109</v>
       </c>
-      <c r="S188" s="1">
+      <c r="S188" s="2">
         <v>46049</v>
       </c>
-      <c r="U188" s="1">
+      <c r="U188" s="2">
         <v>46139</v>
       </c>
       <c r="W188" t="s">
@@ -38838,10 +38843,10 @@
       <c r="P189" t="s">
         <v>109</v>
       </c>
-      <c r="S189" s="1">
+      <c r="S189" s="2">
         <v>46049</v>
       </c>
-      <c r="U189" s="1">
+      <c r="U189" s="2">
         <v>46139</v>
       </c>
       <c r="W189" t="s">
@@ -39029,10 +39034,10 @@
       <c r="P190" t="s">
         <v>109</v>
       </c>
-      <c r="S190" s="1">
+      <c r="S190" s="2">
         <v>46049</v>
       </c>
-      <c r="U190" s="1">
+      <c r="U190" s="2">
         <v>46139</v>
       </c>
       <c r="W190" t="s">
@@ -39220,10 +39225,10 @@
       <c r="P191" t="s">
         <v>109</v>
       </c>
-      <c r="S191" s="1">
+      <c r="S191" s="2">
         <v>46049</v>
       </c>
-      <c r="U191" s="1">
+      <c r="U191" s="2">
         <v>46139</v>
       </c>
       <c r="W191" t="s">
@@ -39408,10 +39413,10 @@
       <c r="P192" t="s">
         <v>286</v>
       </c>
-      <c r="S192" s="1">
+      <c r="S192" s="2">
         <v>46015</v>
       </c>
-      <c r="U192" s="1">
+      <c r="U192" s="2">
         <v>46104</v>
       </c>
       <c r="W192" t="s">
@@ -39790,10 +39795,10 @@
       <c r="P194" t="s">
         <v>845</v>
       </c>
-      <c r="S194" s="1">
+      <c r="S194" s="2">
         <v>46154</v>
       </c>
-      <c r="U194" s="1">
+      <c r="U194" s="2">
         <v>46246</v>
       </c>
       <c r="V194">
@@ -39975,10 +39980,10 @@
       <c r="P195" t="s">
         <v>845</v>
       </c>
-      <c r="S195" s="1">
+      <c r="S195" s="2">
         <v>46140</v>
       </c>
-      <c r="U195" s="1">
+      <c r="U195" s="2">
         <v>46231</v>
       </c>
       <c r="V195">
@@ -40163,10 +40168,10 @@
       <c r="P196" t="s">
         <v>109</v>
       </c>
-      <c r="S196" s="1">
+      <c r="S196" s="2">
         <v>46140</v>
       </c>
-      <c r="U196" s="1">
+      <c r="U196" s="2">
         <v>46224</v>
       </c>
       <c r="V196">
@@ -40345,10 +40350,10 @@
       <c r="P197" t="s">
         <v>286</v>
       </c>
-      <c r="S197" s="1">
+      <c r="S197" s="2">
         <v>46077</v>
       </c>
-      <c r="U197" s="1">
+      <c r="U197" s="2">
         <v>46166</v>
       </c>
       <c r="W197" t="s">
@@ -40515,10 +40520,10 @@
       <c r="P198" t="s">
         <v>191</v>
       </c>
-      <c r="S198" s="1">
+      <c r="S198" s="2">
         <v>46106</v>
       </c>
-      <c r="U198" s="1">
+      <c r="U198" s="2">
         <v>46198</v>
       </c>
       <c r="W198" t="s">
@@ -40700,10 +40705,10 @@
       <c r="P199" t="s">
         <v>109</v>
       </c>
-      <c r="S199" s="1">
+      <c r="S199" s="2">
         <v>46138</v>
       </c>
-      <c r="U199" s="1">
+      <c r="U199" s="2">
         <v>46198</v>
       </c>
       <c r="W199" t="s">
@@ -40873,10 +40878,10 @@
       <c r="P200" t="s">
         <v>109</v>
       </c>
-      <c r="S200" s="1">
+      <c r="S200" s="2">
         <v>46138</v>
       </c>
-      <c r="U200" s="1">
+      <c r="U200" s="2">
         <v>46198</v>
       </c>
       <c r="W200" t="s">
@@ -41037,10 +41042,10 @@
       <c r="P201" t="s">
         <v>109</v>
       </c>
-      <c r="S201" s="1">
+      <c r="S201" s="2">
         <v>46138</v>
       </c>
-      <c r="U201" s="1">
+      <c r="U201" s="2">
         <v>46198</v>
       </c>
       <c r="W201" t="s">
@@ -41195,10 +41200,10 @@
       <c r="P202" t="s">
         <v>191</v>
       </c>
-      <c r="S202" s="1">
+      <c r="S202" s="2">
         <v>46107</v>
       </c>
-      <c r="U202" s="1">
+      <c r="U202" s="2">
         <v>46199</v>
       </c>
       <c r="V202">
@@ -42427,10 +42432,10 @@
       <c r="P209" t="s">
         <v>191</v>
       </c>
-      <c r="S209" s="1">
+      <c r="S209" s="2">
         <v>46078</v>
       </c>
-      <c r="U209" s="1">
+      <c r="U209" s="2">
         <v>46167</v>
       </c>
       <c r="V209">
@@ -42624,10 +42629,10 @@
       <c r="P210" t="s">
         <v>109</v>
       </c>
-      <c r="S210" s="1">
+      <c r="S210" s="2">
         <v>46073</v>
       </c>
-      <c r="U210" s="1">
+      <c r="U210" s="2">
         <v>46162</v>
       </c>
       <c r="V210">
@@ -43146,10 +43151,10 @@
       <c r="P213" t="s">
         <v>191</v>
       </c>
-      <c r="S213" s="1">
+      <c r="S213" s="2">
         <v>46077</v>
       </c>
-      <c r="U213" s="1">
+      <c r="U213" s="2">
         <v>46166</v>
       </c>
       <c r="V213">
@@ -44987,10 +44992,10 @@
       <c r="P223" t="s">
         <v>109</v>
       </c>
-      <c r="S223" s="1">
+      <c r="S223" s="2">
         <v>46078</v>
       </c>
-      <c r="U223" s="1">
+      <c r="U223" s="2">
         <v>46167</v>
       </c>
       <c r="V223">
@@ -45178,10 +45183,10 @@
       <c r="P224" t="s">
         <v>191</v>
       </c>
-      <c r="S224" s="1">
+      <c r="S224" s="2">
         <v>46077</v>
       </c>
-      <c r="U224" s="1">
+      <c r="U224" s="2">
         <v>46166</v>
       </c>
       <c r="V224">
@@ -45360,10 +45365,10 @@
       <c r="P225" t="s">
         <v>109</v>
       </c>
-      <c r="S225" s="1">
+      <c r="S225" s="2">
         <v>46077</v>
       </c>
-      <c r="U225" s="1">
+      <c r="U225" s="2">
         <v>46166</v>
       </c>
       <c r="V225">
@@ -45554,10 +45559,10 @@
       <c r="P226" t="s">
         <v>109</v>
       </c>
-      <c r="S226" s="1">
+      <c r="S226" s="2">
         <v>46024</v>
       </c>
-      <c r="U226" s="1">
+      <c r="U226" s="2">
         <v>46111</v>
       </c>
       <c r="V226">
@@ -45748,10 +45753,10 @@
       <c r="R227">
         <v>568.79999999999995</v>
       </c>
-      <c r="S227" s="1">
+      <c r="S227" s="2">
         <v>46069</v>
       </c>
-      <c r="U227" s="1">
+      <c r="U227" s="2">
         <v>46160</v>
       </c>
       <c r="V227">
@@ -45948,10 +45953,10 @@
       <c r="R228">
         <v>711</v>
       </c>
-      <c r="S228" s="1">
+      <c r="S228" s="2">
         <v>46069</v>
       </c>
-      <c r="U228" s="1">
+      <c r="U228" s="2">
         <v>46160</v>
       </c>
       <c r="V228">
@@ -46867,10 +46872,10 @@
       <c r="P233" t="s">
         <v>191</v>
       </c>
-      <c r="S233" s="1">
+      <c r="S233" s="2">
         <v>46035</v>
       </c>
-      <c r="U233" s="1">
+      <c r="U233" s="2">
         <v>46125</v>
       </c>
       <c r="V233">
@@ -47070,10 +47075,10 @@
       <c r="P234" t="s">
         <v>191</v>
       </c>
-      <c r="S234" s="1">
+      <c r="S234" s="2">
         <v>46049</v>
       </c>
-      <c r="U234" s="1">
+      <c r="U234" s="2">
         <v>46139</v>
       </c>
       <c r="V234">
@@ -47613,10 +47618,10 @@
       <c r="P237" t="s">
         <v>191</v>
       </c>
-      <c r="S237" s="1">
+      <c r="S237" s="2">
         <v>45982</v>
       </c>
-      <c r="U237" s="1">
+      <c r="U237" s="2">
         <v>46074</v>
       </c>
       <c r="V237">
@@ -47810,10 +47815,10 @@
       <c r="P238" t="s">
         <v>191</v>
       </c>
-      <c r="S238" s="1">
+      <c r="S238" s="2">
         <v>45975</v>
       </c>
-      <c r="U238" s="1">
+      <c r="U238" s="2">
         <v>46066</v>
       </c>
       <c r="V238">
@@ -48022,10 +48027,10 @@
       <c r="P239" t="s">
         <v>109</v>
       </c>
-      <c r="S239" s="1">
+      <c r="S239" s="2">
         <v>45958</v>
       </c>
-      <c r="U239" s="1">
+      <c r="U239" s="2">
         <v>46078</v>
       </c>
       <c r="V239">
@@ -48198,10 +48203,10 @@
       <c r="P240" t="s">
         <v>109</v>
       </c>
-      <c r="S240" s="1">
+      <c r="S240" s="2">
         <v>45979</v>
       </c>
-      <c r="U240" s="1">
+      <c r="U240" s="2">
         <v>46071</v>
       </c>
       <c r="V240">
@@ -48380,10 +48385,10 @@
       <c r="P241" t="s">
         <v>109</v>
       </c>
-      <c r="S241" s="1">
+      <c r="S241" s="2">
         <v>45979</v>
       </c>
-      <c r="U241" s="1">
+      <c r="U241" s="2">
         <v>46071</v>
       </c>
       <c r="V241">
@@ -48556,10 +48561,10 @@
       <c r="P242" t="s">
         <v>191</v>
       </c>
-      <c r="S242" s="1">
+      <c r="S242" s="2">
         <v>45975</v>
       </c>
-      <c r="U242" s="1">
+      <c r="U242" s="2">
         <v>46066</v>
       </c>
       <c r="V242">
@@ -48759,10 +48764,10 @@
       <c r="P243" t="s">
         <v>109</v>
       </c>
-      <c r="S243" s="1">
+      <c r="S243" s="2">
         <v>45975</v>
       </c>
-      <c r="U243" s="1">
+      <c r="U243" s="2">
         <v>46066</v>
       </c>
       <c r="V243">
@@ -48959,10 +48964,10 @@
       <c r="P244" t="s">
         <v>191</v>
       </c>
-      <c r="S244" s="1">
+      <c r="S244" s="2">
         <v>45957</v>
       </c>
-      <c r="U244" s="1">
+      <c r="U244" s="2">
         <v>46050</v>
       </c>
       <c r="V244">
@@ -49162,10 +49167,10 @@
       <c r="P245" t="s">
         <v>191</v>
       </c>
-      <c r="S245" s="1">
+      <c r="S245" s="2">
         <v>45953</v>
       </c>
-      <c r="U245" s="1">
+      <c r="U245" s="2">
         <v>46045</v>
       </c>
       <c r="W245" t="s">
@@ -49923,10 +49928,10 @@
       <c r="P249" t="s">
         <v>191</v>
       </c>
-      <c r="S249" s="1">
+      <c r="S249" s="2">
         <v>45922</v>
       </c>
-      <c r="U249" s="1">
+      <c r="U249" s="2">
         <v>46023</v>
       </c>
       <c r="V249">
@@ -50132,7 +50137,7 @@
       <c r="P250" t="s">
         <v>109</v>
       </c>
-      <c r="S250" s="1">
+      <c r="S250" s="2">
         <v>45889</v>
       </c>
       <c r="V250">
@@ -53826,10 +53831,10 @@
       <c r="P270" t="s">
         <v>199</v>
       </c>
-      <c r="S270" s="1">
+      <c r="S270" s="2">
         <v>46078</v>
       </c>
-      <c r="U270" s="1">
+      <c r="U270" s="2">
         <v>46167</v>
       </c>
       <c r="V270">
@@ -54023,10 +54028,10 @@
       <c r="P271" t="s">
         <v>109</v>
       </c>
-      <c r="S271" s="1">
+      <c r="S271" s="2">
         <v>46078</v>
       </c>
-      <c r="U271" s="1">
+      <c r="U271" s="2">
         <v>46167</v>
       </c>
       <c r="V271">
@@ -54214,10 +54219,10 @@
       <c r="P272" t="s">
         <v>109</v>
       </c>
-      <c r="S272" s="1">
+      <c r="S272" s="2">
         <v>46078</v>
       </c>
-      <c r="U272" s="1">
+      <c r="U272" s="2">
         <v>46166</v>
       </c>
       <c r="V272">
@@ -54405,10 +54410,10 @@
       <c r="P273" t="s">
         <v>109</v>
       </c>
-      <c r="S273" s="1">
+      <c r="S273" s="2">
         <v>46078</v>
       </c>
-      <c r="U273" s="1">
+      <c r="U273" s="2">
         <v>46166</v>
       </c>
       <c r="V273">
@@ -54596,10 +54601,10 @@
       <c r="P274" t="s">
         <v>109</v>
       </c>
-      <c r="S274" s="1">
+      <c r="S274" s="2">
         <v>46078</v>
       </c>
-      <c r="U274" s="1">
+      <c r="U274" s="2">
         <v>46166</v>
       </c>
       <c r="V274">
@@ -54787,10 +54792,10 @@
       <c r="P275" t="s">
         <v>109</v>
       </c>
-      <c r="S275" s="1">
+      <c r="S275" s="2">
         <v>46063</v>
       </c>
-      <c r="U275" s="1">
+      <c r="U275" s="2">
         <v>46146</v>
       </c>
       <c r="V275">
@@ -54996,10 +55001,10 @@
       <c r="P276" t="s">
         <v>109</v>
       </c>
-      <c r="S276" s="1">
+      <c r="S276" s="2">
         <v>46045</v>
       </c>
-      <c r="U276" s="1">
+      <c r="U276" s="2">
         <v>46135</v>
       </c>
       <c r="V276">
@@ -55199,10 +55204,10 @@
       <c r="P277" t="s">
         <v>109</v>
       </c>
-      <c r="S277" s="1">
+      <c r="S277" s="2">
         <v>46045</v>
       </c>
-      <c r="U277" s="1">
+      <c r="U277" s="2">
         <v>46135</v>
       </c>
       <c r="V277">
@@ -55402,10 +55407,10 @@
       <c r="P278" t="s">
         <v>109</v>
       </c>
-      <c r="S278" s="1">
+      <c r="S278" s="2">
         <v>46063</v>
       </c>
-      <c r="U278" s="1">
+      <c r="U278" s="2">
         <v>46146</v>
       </c>
       <c r="V278">
@@ -55605,10 +55610,10 @@
       <c r="P279" t="s">
         <v>109</v>
       </c>
-      <c r="S279" s="1">
+      <c r="S279" s="2">
         <v>46063</v>
       </c>
-      <c r="U279" s="1">
+      <c r="U279" s="2">
         <v>46146</v>
       </c>
       <c r="V279">
@@ -55811,10 +55816,10 @@
       <c r="P280" t="s">
         <v>109</v>
       </c>
-      <c r="S280" s="1">
+      <c r="S280" s="2">
         <v>46063</v>
       </c>
-      <c r="U280" s="1">
+      <c r="U280" s="2">
         <v>46146</v>
       </c>
       <c r="V280">
@@ -56014,10 +56019,10 @@
       <c r="P281" t="s">
         <v>109</v>
       </c>
-      <c r="S281" s="1">
+      <c r="S281" s="2">
         <v>46063</v>
       </c>
-      <c r="U281" s="1">
+      <c r="U281" s="2">
         <v>46146</v>
       </c>
       <c r="V281">
@@ -57202,10 +57207,10 @@
       <c r="P287" t="s">
         <v>109</v>
       </c>
-      <c r="S287" s="1">
+      <c r="S287" s="2">
         <v>46049</v>
       </c>
-      <c r="U287" s="1">
+      <c r="U287" s="2">
         <v>46139</v>
       </c>
       <c r="V287">
@@ -57405,10 +57410,10 @@
       <c r="P288" t="s">
         <v>286</v>
       </c>
-      <c r="S288" s="1">
+      <c r="S288" s="2">
         <v>46035</v>
       </c>
-      <c r="U288" s="1">
+      <c r="U288" s="2">
         <v>46125</v>
       </c>
       <c r="V288">
@@ -57793,10 +57798,10 @@
       <c r="R290">
         <v>2.56</v>
       </c>
-      <c r="S290" s="1">
+      <c r="S290" s="2">
         <v>46038</v>
       </c>
-      <c r="U290" s="1">
+      <c r="U290" s="2">
         <v>46149</v>
       </c>
       <c r="V290">
@@ -58011,10 +58016,10 @@
       <c r="R291">
         <v>2.74</v>
       </c>
-      <c r="S291" s="1">
+      <c r="S291" s="2">
         <v>46038</v>
       </c>
-      <c r="U291" s="1">
+      <c r="U291" s="2">
         <v>46149</v>
       </c>
       <c r="V291">
@@ -58226,10 +58231,10 @@
       <c r="R292">
         <v>16.21</v>
       </c>
-      <c r="S292" s="1">
+      <c r="S292" s="2">
         <v>46045</v>
       </c>
-      <c r="U292" s="1">
+      <c r="U292" s="2">
         <v>46157</v>
       </c>
       <c r="V292">
@@ -59309,10 +59314,10 @@
       <c r="P298" t="s">
         <v>191</v>
       </c>
-      <c r="S298" s="1">
+      <c r="S298" s="2">
         <v>46015</v>
       </c>
-      <c r="U298" s="1">
+      <c r="U298" s="2">
         <v>46105</v>
       </c>
       <c r="V298">
@@ -59515,10 +59520,10 @@
       <c r="P299" t="s">
         <v>191</v>
       </c>
-      <c r="S299" s="1">
+      <c r="S299" s="2">
         <v>46015</v>
       </c>
-      <c r="U299" s="1">
+      <c r="U299" s="2">
         <v>46105</v>
       </c>
       <c r="V299">
@@ -61527,10 +61532,10 @@
       <c r="R309">
         <v>4.1340000000000003</v>
       </c>
-      <c r="S309" s="1">
+      <c r="S309" s="2">
         <v>45992</v>
       </c>
-      <c r="U309" s="1">
+      <c r="U309" s="2">
         <v>46076</v>
       </c>
       <c r="V309">
@@ -61748,10 +61753,10 @@
       <c r="R310">
         <v>31.771999999999998</v>
       </c>
-      <c r="S310" s="1">
+      <c r="S310" s="2">
         <v>45992</v>
       </c>
-      <c r="U310" s="1">
+      <c r="U310" s="2">
         <v>46076</v>
       </c>
       <c r="V310">
@@ -61963,10 +61968,10 @@
       <c r="R311">
         <v>15.88</v>
       </c>
-      <c r="S311" s="1">
+      <c r="S311" s="2">
         <v>45992</v>
       </c>
-      <c r="U311" s="1">
+      <c r="U311" s="2">
         <v>46076</v>
       </c>
       <c r="V311">
@@ -62166,10 +62171,10 @@
       <c r="P312" t="s">
         <v>191</v>
       </c>
-      <c r="S312" s="1">
+      <c r="S312" s="2">
         <v>45982</v>
       </c>
-      <c r="U312" s="1">
+      <c r="U312" s="2">
         <v>46074</v>
       </c>
       <c r="V312">
@@ -62372,10 +62377,10 @@
       <c r="R313">
         <v>10.62</v>
       </c>
-      <c r="S313" s="1">
+      <c r="S313" s="2">
         <v>45981</v>
       </c>
-      <c r="U313" s="1">
+      <c r="U313" s="2">
         <v>46068</v>
       </c>
       <c r="V313">
@@ -62596,10 +62601,10 @@
       <c r="R314">
         <v>9.61</v>
       </c>
-      <c r="S314" s="1">
+      <c r="S314" s="2">
         <v>45981</v>
       </c>
-      <c r="U314" s="1">
+      <c r="U314" s="2">
         <v>46068</v>
       </c>
       <c r="V314">
@@ -62796,10 +62801,10 @@
       <c r="P315" t="s">
         <v>191</v>
       </c>
-      <c r="S315" s="1">
+      <c r="S315" s="2">
         <v>45953</v>
       </c>
-      <c r="U315" s="1">
+      <c r="U315" s="2">
         <v>46045</v>
       </c>
       <c r="V315">
@@ -62993,10 +62998,10 @@
       <c r="P316" t="s">
         <v>191</v>
       </c>
-      <c r="S316" s="1">
+      <c r="S316" s="2">
         <v>45982</v>
       </c>
-      <c r="U316" s="1">
+      <c r="U316" s="2">
         <v>46074</v>
       </c>
       <c r="V316">
@@ -63184,10 +63189,10 @@
       <c r="P317" t="s">
         <v>191</v>
       </c>
-      <c r="S317" s="1">
+      <c r="S317" s="2">
         <v>45982</v>
       </c>
-      <c r="U317" s="1">
+      <c r="U317" s="2">
         <v>46074</v>
       </c>
       <c r="V317">
@@ -63575,10 +63580,10 @@
       <c r="P319" t="s">
         <v>199</v>
       </c>
-      <c r="S319" s="1">
+      <c r="S319" s="2">
         <v>45953</v>
       </c>
-      <c r="U319" s="1">
+      <c r="U319" s="2">
         <v>46045</v>
       </c>
       <c r="W319" t="s">
@@ -64142,10 +64147,10 @@
       <c r="P322" t="s">
         <v>199</v>
       </c>
-      <c r="S322" s="1">
+      <c r="S322" s="2">
         <v>45972</v>
       </c>
-      <c r="U322" s="1">
+      <c r="U322" s="2">
         <v>46064</v>
       </c>
       <c r="W322" t="s">
@@ -64518,10 +64523,10 @@
       <c r="P324" t="s">
         <v>109</v>
       </c>
-      <c r="S324" s="1">
+      <c r="S324" s="2">
         <v>45953</v>
       </c>
-      <c r="U324" s="1">
+      <c r="U324" s="2">
         <v>46045</v>
       </c>
       <c r="W324" t="s">
@@ -64709,10 +64714,10 @@
       <c r="P325" t="s">
         <v>199</v>
       </c>
-      <c r="S325" s="1">
+      <c r="S325" s="2">
         <v>45953</v>
       </c>
-      <c r="U325" s="1">
+      <c r="U325" s="2">
         <v>46045</v>
       </c>
       <c r="W325" t="s">
@@ -64921,13 +64926,13 @@
       <c r="R326">
         <v>2.56</v>
       </c>
-      <c r="S326" s="1">
+      <c r="S326" s="2">
         <v>45953</v>
       </c>
       <c r="T326" s="1">
         <v>45954</v>
       </c>
-      <c r="U326" s="1">
+      <c r="U326" s="2">
         <v>46036</v>
       </c>
       <c r="V326">
@@ -65330,7 +65335,7 @@
       <c r="R328">
         <v>13.86</v>
       </c>
-      <c r="S328" t="s">
+      <c r="S328" s="2" t="s">
         <v>1350</v>
       </c>
       <c r="T328" s="1">
@@ -65554,13 +65559,13 @@
       <c r="R329">
         <v>3.95</v>
       </c>
-      <c r="S329" s="1">
+      <c r="S329" s="2">
         <v>45946</v>
       </c>
       <c r="T329" s="1">
         <v>45946</v>
       </c>
-      <c r="U329" s="1">
+      <c r="U329" s="2">
         <v>46028</v>
       </c>
       <c r="V329">
@@ -65787,13 +65792,13 @@
       <c r="R330">
         <v>3.95</v>
       </c>
-      <c r="S330" s="1">
+      <c r="S330" s="2">
         <v>45946</v>
       </c>
       <c r="T330" s="1">
         <v>45946</v>
       </c>
-      <c r="U330" s="1">
+      <c r="U330" s="2">
         <v>46028</v>
       </c>
       <c r="V330">
@@ -70028,10 +70033,10 @@
       <c r="P355" t="s">
         <v>286</v>
       </c>
-      <c r="S355" s="1">
+      <c r="S355" s="2">
         <v>46073</v>
       </c>
-      <c r="U355" s="1">
+      <c r="U355" s="2">
         <v>46087</v>
       </c>
       <c r="W355" t="s">
@@ -70168,10 +70173,10 @@
       <c r="P356" t="s">
         <v>286</v>
       </c>
-      <c r="S356" s="1">
+      <c r="S356" s="2">
         <v>46073</v>
       </c>
-      <c r="U356" s="1">
+      <c r="U356" s="2">
         <v>46087</v>
       </c>
       <c r="W356" t="s">
@@ -70302,10 +70307,10 @@
       <c r="P357" t="s">
         <v>845</v>
       </c>
-      <c r="S357" s="1">
+      <c r="S357" s="2">
         <v>46140</v>
       </c>
-      <c r="U357" s="1">
+      <c r="U357" s="2">
         <v>46231</v>
       </c>
       <c r="V357">
@@ -70475,10 +70480,10 @@
       <c r="P358" t="s">
         <v>845</v>
       </c>
-      <c r="S358" s="1">
+      <c r="S358" s="2">
         <v>46162</v>
       </c>
-      <c r="U358" s="1">
+      <c r="U358" s="2">
         <v>46254</v>
       </c>
       <c r="W358" t="s">
@@ -70636,10 +70641,10 @@
       <c r="P359" t="s">
         <v>286</v>
       </c>
-      <c r="S359" s="1">
+      <c r="S359" s="2">
         <v>46140</v>
       </c>
-      <c r="U359" s="1">
+      <c r="U359" s="2">
         <v>46231</v>
       </c>
       <c r="W359" t="s">
@@ -70809,10 +70814,10 @@
       <c r="P360" t="s">
         <v>616</v>
       </c>
-      <c r="S360" s="1">
+      <c r="S360" s="2">
         <v>46153</v>
       </c>
-      <c r="U360" s="1">
+      <c r="U360" s="2">
         <v>46174</v>
       </c>
       <c r="V360">
@@ -70979,10 +70984,10 @@
       <c r="P361" t="s">
         <v>109</v>
       </c>
-      <c r="S361" s="1">
+      <c r="S361" s="2">
         <v>46114</v>
       </c>
-      <c r="U361" s="1">
+      <c r="U361" s="2">
         <v>46130</v>
       </c>
       <c r="V361">
@@ -71149,10 +71154,10 @@
       <c r="P362" t="s">
         <v>845</v>
       </c>
-      <c r="S362" s="1">
+      <c r="S362" s="2">
         <v>46139</v>
       </c>
-      <c r="U362" s="1">
+      <c r="U362" s="2">
         <v>46230</v>
       </c>
       <c r="V362">
@@ -71358,10 +71363,10 @@
       <c r="R363">
         <v>14.7698</v>
       </c>
-      <c r="S363" s="1">
+      <c r="S363" s="2">
         <v>46175</v>
       </c>
-      <c r="U363" s="1">
+      <c r="U363" s="2">
         <v>46259</v>
       </c>
       <c r="V363">
@@ -71549,10 +71554,10 @@
       <c r="R364">
         <v>2.4542999999999999</v>
       </c>
-      <c r="S364" s="1">
+      <c r="S364" s="2">
         <v>46175</v>
       </c>
-      <c r="U364" s="1">
+      <c r="U364" s="2">
         <v>46259</v>
       </c>
       <c r="V364">
@@ -71734,10 +71739,10 @@
       <c r="R365">
         <v>7.4737999999999998</v>
       </c>
-      <c r="S365" s="1">
+      <c r="S365" s="2">
         <v>46175</v>
       </c>
-      <c r="U365" s="1">
+      <c r="U365" s="2">
         <v>46259</v>
       </c>
       <c r="V365">
@@ -71919,10 +71924,10 @@
       <c r="R366">
         <v>5.8940000000000001</v>
       </c>
-      <c r="S366" s="1">
+      <c r="S366" s="2">
         <v>46176</v>
       </c>
-      <c r="U366" s="1">
+      <c r="U366" s="2">
         <v>46260</v>
       </c>
       <c r="V366">
@@ -72104,10 +72109,10 @@
       <c r="R367">
         <v>6.9160000000000004</v>
       </c>
-      <c r="S367" s="1">
+      <c r="S367" s="2">
         <v>46181</v>
       </c>
-      <c r="U367" s="1">
+      <c r="U367" s="2">
         <v>46265</v>
       </c>
       <c r="V367">
@@ -72289,10 +72294,10 @@
       <c r="R368">
         <v>4.9669999999999996</v>
       </c>
-      <c r="S368" s="1">
+      <c r="S368" s="2">
         <v>46181</v>
       </c>
-      <c r="U368" s="1">
+      <c r="U368" s="2">
         <v>46265</v>
       </c>
       <c r="V368">
@@ -72474,10 +72479,10 @@
       <c r="R369">
         <v>4.88</v>
       </c>
-      <c r="S369" s="1">
+      <c r="S369" s="2">
         <v>46181</v>
       </c>
-      <c r="U369" s="1">
+      <c r="U369" s="2">
         <v>46265</v>
       </c>
       <c r="V369">
@@ -72659,10 +72664,10 @@
       <c r="R370">
         <v>8.3580000000000005</v>
       </c>
-      <c r="S370" s="1">
+      <c r="S370" s="2">
         <v>46183</v>
       </c>
-      <c r="U370" s="1">
+      <c r="U370" s="2">
         <v>46267</v>
       </c>
       <c r="V370">
@@ -72847,10 +72852,10 @@
       <c r="R371">
         <v>12.394</v>
       </c>
-      <c r="S371" s="1">
+      <c r="S371" s="2">
         <v>46182</v>
       </c>
-      <c r="U371" s="1">
+      <c r="U371" s="2">
         <v>46266</v>
       </c>
       <c r="V371">
@@ -73029,10 +73034,10 @@
       <c r="R372">
         <v>6.1970000000000001</v>
       </c>
-      <c r="S372" s="1">
+      <c r="S372" s="2">
         <v>46182</v>
       </c>
-      <c r="U372" s="1">
+      <c r="U372" s="2">
         <v>46266</v>
       </c>
       <c r="V372">
@@ -73211,10 +73216,10 @@
       <c r="R373">
         <v>1.2390000000000001</v>
       </c>
-      <c r="S373" s="1">
+      <c r="S373" s="2">
         <v>46183</v>
       </c>
-      <c r="U373" s="1">
+      <c r="U373" s="2">
         <v>46267</v>
       </c>
       <c r="V373">
@@ -73393,10 +73398,10 @@
       <c r="R374">
         <v>9.3640000000000008</v>
       </c>
-      <c r="S374" s="1">
+      <c r="S374" s="2">
         <v>46189</v>
       </c>
-      <c r="U374" s="1">
+      <c r="U374" s="2">
         <v>46273</v>
       </c>
       <c r="V374">
@@ -73575,10 +73580,10 @@
       <c r="R375">
         <v>5.1778000000000004</v>
       </c>
-      <c r="S375" s="1">
+      <c r="S375" s="2">
         <v>46185</v>
       </c>
-      <c r="U375" s="1">
+      <c r="U375" s="2">
         <v>46269</v>
       </c>
       <c r="V375">
@@ -73748,10 +73753,10 @@
       <c r="R376">
         <v>4.28</v>
       </c>
-      <c r="S376" s="1">
+      <c r="S376" s="2">
         <v>46192</v>
       </c>
-      <c r="U376" s="1">
+      <c r="U376" s="2">
         <v>46276</v>
       </c>
       <c r="V376">
@@ -73930,10 +73935,10 @@
       <c r="R377">
         <v>131.166</v>
       </c>
-      <c r="S377" s="1">
+      <c r="S377" s="2">
         <v>46190</v>
       </c>
-      <c r="U377" s="1">
+      <c r="U377" s="2">
         <v>46274</v>
       </c>
       <c r="V377">
@@ -74118,10 +74123,10 @@
       <c r="R378">
         <v>28.401</v>
       </c>
-      <c r="S378" s="1">
+      <c r="S378" s="2">
         <v>46203</v>
       </c>
-      <c r="U378" s="1">
+      <c r="U378" s="2">
         <v>46287</v>
       </c>
       <c r="V378">
@@ -75069,10 +75074,10 @@
       <c r="P384" t="s">
         <v>845</v>
       </c>
-      <c r="S384" s="1">
+      <c r="S384" s="2">
         <v>46140</v>
       </c>
-      <c r="U384" s="1">
+      <c r="U384" s="2">
         <v>46231</v>
       </c>
       <c r="V384">
@@ -75257,10 +75262,10 @@
       <c r="P385" t="s">
         <v>845</v>
       </c>
-      <c r="S385" s="1">
+      <c r="S385" s="2">
         <v>46139</v>
       </c>
-      <c r="U385" s="1">
+      <c r="U385" s="2">
         <v>46230</v>
       </c>
       <c r="V385">
@@ -75439,10 +75444,10 @@
       <c r="P386" t="s">
         <v>109</v>
       </c>
-      <c r="S386" s="1">
+      <c r="S386" s="2">
         <v>46127</v>
       </c>
-      <c r="U386" s="1">
+      <c r="U386" s="2">
         <v>46142</v>
       </c>
       <c r="V386">
@@ -75883,10 +75888,10 @@
       <c r="P389" t="s">
         <v>109</v>
       </c>
-      <c r="S389" s="1">
+      <c r="S389" s="2">
         <v>46091</v>
       </c>
-      <c r="U389" s="1">
+      <c r="U389" s="2">
         <v>46183</v>
       </c>
       <c r="V389">
@@ -76080,10 +76085,10 @@
       <c r="P390" t="s">
         <v>286</v>
       </c>
-      <c r="S390" s="1">
+      <c r="S390" s="2">
         <v>46078</v>
       </c>
-      <c r="U390" s="1">
+      <c r="U390" s="2">
         <v>46167</v>
       </c>
       <c r="V390">
@@ -76277,10 +76282,10 @@
       <c r="P391" t="s">
         <v>199</v>
       </c>
-      <c r="S391" s="1">
+      <c r="S391" s="2">
         <v>46139</v>
       </c>
-      <c r="U391" s="1">
+      <c r="U391" s="2">
         <v>46230</v>
       </c>
       <c r="W391" t="s">
@@ -76450,10 +76455,10 @@
       <c r="P392" t="s">
         <v>199</v>
       </c>
-      <c r="S392" s="1">
+      <c r="S392" s="2">
         <v>46154</v>
       </c>
-      <c r="U392" s="1">
+      <c r="U392" s="2">
         <v>46246</v>
       </c>
       <c r="W392" t="s">
@@ -76623,10 +76628,10 @@
       <c r="P393" t="s">
         <v>199</v>
       </c>
-      <c r="S393" s="1">
+      <c r="S393" s="2">
         <v>46139</v>
       </c>
-      <c r="U393" s="1">
+      <c r="U393" s="2">
         <v>46230</v>
       </c>
       <c r="W393" t="s">
@@ -76796,10 +76801,10 @@
       <c r="P394" t="s">
         <v>109</v>
       </c>
-      <c r="S394" s="1">
+      <c r="S394" s="2">
         <v>46140</v>
       </c>
-      <c r="U394" s="1">
+      <c r="U394" s="2">
         <v>46231</v>
       </c>
       <c r="V394">
@@ -76972,10 +76977,10 @@
       <c r="P395" t="s">
         <v>109</v>
       </c>
-      <c r="S395" s="1">
+      <c r="S395" s="2">
         <v>46154</v>
       </c>
-      <c r="U395" s="1">
+      <c r="U395" s="2">
         <v>46246</v>
       </c>
       <c r="V395">
@@ -77148,10 +77153,10 @@
       <c r="P396" t="s">
         <v>109</v>
       </c>
-      <c r="S396" s="1">
+      <c r="S396" s="2">
         <v>46164</v>
       </c>
-      <c r="U396" s="1">
+      <c r="U396" s="2">
         <v>46213</v>
       </c>
       <c r="V396">
@@ -77291,10 +77296,10 @@
       <c r="P397" t="s">
         <v>109</v>
       </c>
-      <c r="S397" s="1">
+      <c r="S397" s="2">
         <v>46162</v>
       </c>
-      <c r="U397" s="1">
+      <c r="U397" s="2">
         <v>46254</v>
       </c>
       <c r="V397">
@@ -77440,10 +77445,10 @@
       <c r="P398" t="s">
         <v>109</v>
       </c>
-      <c r="S398" s="1">
+      <c r="S398" s="2">
         <v>46154</v>
       </c>
-      <c r="U398" s="1">
+      <c r="U398" s="2">
         <v>46246</v>
       </c>
       <c r="V398">
@@ -79774,10 +79779,10 @@
       <c r="P416" t="s">
         <v>109</v>
       </c>
-      <c r="S416" s="1">
+      <c r="S416" s="2">
         <v>46154</v>
       </c>
-      <c r="U416" s="1">
+      <c r="U416" s="2">
         <v>46246</v>
       </c>
       <c r="W416" t="s">
@@ -79929,10 +79934,10 @@
       <c r="P417" t="s">
         <v>191</v>
       </c>
-      <c r="S417" s="1">
+      <c r="S417" s="2">
         <v>46162</v>
       </c>
-      <c r="U417" s="1">
+      <c r="U417" s="2">
         <v>46254</v>
       </c>
       <c r="W417" t="s">
@@ -80075,10 +80080,10 @@
       <c r="P418" t="s">
         <v>191</v>
       </c>
-      <c r="S418" s="1">
+      <c r="S418" s="2">
         <v>46154</v>
       </c>
-      <c r="U418" s="1">
+      <c r="U418" s="2">
         <v>46246</v>
       </c>
       <c r="V418">
@@ -80224,10 +80229,10 @@
       <c r="P419" t="s">
         <v>191</v>
       </c>
-      <c r="S419" s="1">
+      <c r="S419" s="2">
         <v>46140</v>
       </c>
-      <c r="U419" s="1">
+      <c r="U419" s="2">
         <v>46231</v>
       </c>
       <c r="V419">
@@ -80370,10 +80375,10 @@
       <c r="P420" t="s">
         <v>109</v>
       </c>
-      <c r="S420" s="1">
+      <c r="S420" s="2">
         <v>46140</v>
       </c>
-      <c r="U420" s="1">
+      <c r="U420" s="2">
         <v>46231</v>
       </c>
       <c r="V420">
@@ -80513,10 +80518,10 @@
       <c r="P421" t="s">
         <v>109</v>
       </c>
-      <c r="S421" s="1">
+      <c r="S421" s="2">
         <v>46140</v>
       </c>
-      <c r="U421" s="1">
+      <c r="U421" s="2">
         <v>46231</v>
       </c>
       <c r="W421" t="s">
@@ -80665,10 +80670,10 @@
       <c r="P422" t="s">
         <v>109</v>
       </c>
-      <c r="S422" s="1">
+      <c r="S422" s="2">
         <v>46154</v>
       </c>
-      <c r="U422" s="1">
+      <c r="U422" s="2">
         <v>46246</v>
       </c>
       <c r="W422" t="s">
@@ -81091,10 +81096,10 @@
       <c r="P425" t="s">
         <v>109</v>
       </c>
-      <c r="S425" s="1">
+      <c r="S425" s="2">
         <v>46140</v>
       </c>
-      <c r="U425" s="1">
+      <c r="U425" s="2">
         <v>46231</v>
       </c>
       <c r="W425" t="s">
@@ -81237,10 +81242,10 @@
       <c r="P426" t="s">
         <v>109</v>
       </c>
-      <c r="S426" s="1">
+      <c r="S426" s="2">
         <v>46140</v>
       </c>
-      <c r="U426" s="1">
+      <c r="U426" s="2">
         <v>46231</v>
       </c>
       <c r="W426" t="s">
@@ -81383,10 +81388,10 @@
       <c r="P427" t="s">
         <v>109</v>
       </c>
-      <c r="S427" s="1">
+      <c r="S427" s="2">
         <v>46140</v>
       </c>
-      <c r="U427" s="1">
+      <c r="U427" s="2">
         <v>46231</v>
       </c>
       <c r="W427" t="s">
@@ -84070,10 +84075,10 @@
       <c r="R446">
         <v>2.649</v>
       </c>
-      <c r="S446" s="1">
+      <c r="S446" s="2">
         <v>46185</v>
       </c>
-      <c r="U446" s="1">
+      <c r="U446" s="2">
         <v>46227</v>
       </c>
       <c r="W446" t="s">
@@ -84240,10 +84245,10 @@
       <c r="P447" t="s">
         <v>109</v>
       </c>
-      <c r="S447" s="1">
+      <c r="S447" s="2">
         <v>46140</v>
       </c>
-      <c r="U447" s="1">
+      <c r="U447" s="2">
         <v>46231</v>
       </c>
       <c r="V447">
@@ -84404,10 +84409,10 @@
       <c r="P448" t="s">
         <v>109</v>
       </c>
-      <c r="S448" s="1">
+      <c r="S448" s="2">
         <v>46154</v>
       </c>
-      <c r="U448" s="1">
+      <c r="U448" s="2">
         <v>46246</v>
       </c>
       <c r="W448" t="s">
@@ -84550,10 +84555,10 @@
       <c r="P449" t="s">
         <v>109</v>
       </c>
-      <c r="S449" s="1">
+      <c r="S449" s="2">
         <v>46154</v>
       </c>
-      <c r="U449" s="1">
+      <c r="U449" s="2">
         <v>46246</v>
       </c>
       <c r="W449" t="s">
@@ -84690,10 +84695,10 @@
       <c r="P450" t="s">
         <v>109</v>
       </c>
-      <c r="S450" s="1">
+      <c r="S450" s="2">
         <v>46154</v>
       </c>
-      <c r="U450" s="1">
+      <c r="U450" s="2">
         <v>46246</v>
       </c>
       <c r="W450" t="s">
@@ -84827,10 +84832,10 @@
       <c r="P451" t="s">
         <v>191</v>
       </c>
-      <c r="S451" s="1">
+      <c r="S451" s="2">
         <v>46195</v>
       </c>
-      <c r="U451" s="1">
+      <c r="U451" s="2">
         <v>46288</v>
       </c>
       <c r="AI451">
@@ -84919,10 +84924,10 @@
       <c r="P452" t="s">
         <v>199</v>
       </c>
-      <c r="S452" s="1">
+      <c r="S452" s="2">
         <v>46232</v>
       </c>
-      <c r="U452" s="1">
+      <c r="U452" s="2">
         <v>46294</v>
       </c>
       <c r="W452" t="s">
